--- a/exports/SONACOMS_full_report.xlsx
+++ b/exports/SONACOMS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.67</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>740</v>
+        <v>726.35</v>
       </c>
       <c r="I2" t="n">
         <v>728.3084547273294</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0.18</v>
+        <v>-1.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.65</v>
+        <v>2.53</v>
       </c>
       <c r="M2" t="n">
         <v>0.5</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.55208333334</v>
+        <v>44595.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>676.5</v>
+        <v>686.5</v>
       </c>
       <c r="I3" t="n">
         <v>685.8159713183916</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="L3" t="n">
         <v>2.54</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>10.7</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>632.85</v>
+        <v>612.45</v>
       </c>
       <c r="I4" t="n">
         <v>619.6132519745369</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.82</v>
+        <v>-10.79</v>
       </c>
       <c r="L4" t="n">
-        <v>9.390000000000001</v>
+        <v>17.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.79</v>
+        <v>10.16</v>
       </c>
       <c r="N4" t="n">
         <v>5.53</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.91</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>631.25</v>
+        <v>643.95</v>
       </c>
       <c r="I5" t="n">
         <v>633.0807424489999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.07</v>
+        <v>-5.14</v>
       </c>
       <c r="L5" t="n">
         <v>9.01</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.42</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44663.55208333334</v>
+        <v>44664.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>630.5</v>
+        <v>621.3</v>
       </c>
       <c r="I6" t="n">
         <v>630.3581013018339</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.09</v>
+        <v>-3.52</v>
       </c>
       <c r="L6" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="M6" t="n">
         <v>0.5600000000000001</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>7.81</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44671.38541666666</v>
+        <v>44671.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>650</v>
+        <v>661.5</v>
       </c>
       <c r="I7" t="n">
         <v>659.2235900671812</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.62</v>
+        <v>-6.47</v>
       </c>
       <c r="L7" t="n">
-        <v>5.9</v>
+        <v>6.87</v>
       </c>
       <c r="M7" t="n">
         <v>2.56</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44683.55208333334</v>
+        <v>44685.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>631.3</v>
+        <v>620.85</v>
       </c>
       <c r="I8" t="n">
         <v>626.8473681464908</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.57</v>
+        <v>-6.15</v>
       </c>
       <c r="L8" t="n">
-        <v>5.87</v>
+        <v>6.88</v>
       </c>
       <c r="M8" t="n">
         <v>1.44</v>
       </c>
       <c r="N8" t="n">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="O8" t="n">
         <v>5.67</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44719.38541666666</v>
+        <v>44719.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>578.6</v>
+        <v>588</v>
       </c>
       <c r="I9" t="n">
         <v>582.7779742505071</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>6.81</v>
+        <v>5.29</v>
       </c>
       <c r="L9" t="n">
         <v>2.76</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.92</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44728.55208333334</v>
+        <v>44729.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="I10" t="n">
         <v>558.7541288509543</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.72</v>
+        <v>-5.61</v>
       </c>
       <c r="L10" t="n">
-        <v>3.89</v>
+        <v>5.94</v>
       </c>
       <c r="M10" t="n">
         <v>2.17</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.07</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>568.35</v>
+        <v>592.2</v>
       </c>
       <c r="I11" t="n">
         <v>577.0922279319408</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.41</v>
+        <v>-6.7</v>
       </c>
       <c r="L11" t="n">
-        <v>6.7</v>
+        <v>7.82</v>
       </c>
       <c r="M11" t="n">
         <v>1.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="O11" t="n">
         <v>0.52</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.27</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44789.55208333334</v>
+        <v>44790.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>572.45</v>
+        <v>533.3</v>
       </c>
       <c r="I12" t="n">
         <v>559.4940956706215</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.34</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>6.33</v>
+        <v>10.78</v>
       </c>
       <c r="M12" t="n">
         <v>0.16</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>5.84</v>
       </c>
       <c r="O12" t="n">
         <v>4.43</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.19</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44816.55208333334</v>
+        <v>44817.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>525.25</v>
+        <v>542.9</v>
       </c>
       <c r="I13" t="n">
         <v>542.2877558060471</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
-        <v>1.51</v>
+        <v>-1.8</v>
       </c>
       <c r="L13" t="n">
         <v>7.87</v>
@@ -1182,7 +1337,7 @@
         <v>0.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>3.66</v>
       </c>
       <c r="O13" t="n">
         <v>-5.84</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>5.66</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>525.8</v>
+        <v>517.15</v>
       </c>
       <c r="I14" t="n">
         <v>518.5162231945628</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.15</v>
+        <v>-4.74</v>
       </c>
       <c r="L14" t="n">
-        <v>3.48</v>
+        <v>4.84</v>
       </c>
       <c r="M14" t="n">
         <v>1.9</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.52</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44894.55208333334</v>
+        <v>44895.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>451.3</v>
+        <v>457.8</v>
       </c>
       <c r="I15" t="n">
         <v>451.5153363943836</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>74.16666666666667</v>
+        <v>75</v>
       </c>
       <c r="K15" t="n">
-        <v>12.73</v>
+        <v>11.48</v>
       </c>
       <c r="L15" t="n">
         <v>1.59</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>5.69</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44904.38541666666</v>
+        <v>44904.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>443.85</v>
+        <v>440</v>
       </c>
       <c r="I16" t="n">
         <v>441.4112511739295</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.05</v>
+        <v>-3.89</v>
       </c>
       <c r="L16" t="n">
-        <v>3.3</v>
+        <v>4.52</v>
       </c>
       <c r="M16" t="n">
         <v>0.33</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>5.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44908.55208333334</v>
+        <v>44909.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>450.3</v>
+        <v>465.2</v>
       </c>
       <c r="I17" t="n">
         <v>458.3078827943064</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.34</v>
+        <v>-5.73</v>
       </c>
       <c r="L17" t="n">
-        <v>2.73</v>
+        <v>5.86</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="N17" t="n">
-        <v>2.57</v>
+        <v>6.35</v>
       </c>
       <c r="O17" t="n">
         <v>-2.19</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>6.9</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44915.55208333334</v>
+        <v>44916.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>453.4</v>
+        <v>443.3</v>
       </c>
       <c r="I18" t="n">
         <v>444.773612684911</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.54</v>
+        <v>-4.71</v>
       </c>
       <c r="L18" t="n">
-        <v>3.47</v>
+        <v>4.88</v>
       </c>
       <c r="M18" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>3.11</v>
+        <v>3.99</v>
       </c>
       <c r="O18" t="n">
         <v>6.35</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.1</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44935.55208333334</v>
+        <v>44936.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>422.95</v>
+        <v>452.85</v>
       </c>
       <c r="I19" t="n">
         <v>433.3098932599168</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>4.59</v>
+        <v>-2.15</v>
       </c>
       <c r="L19" t="n">
-        <v>3.01</v>
+        <v>3.44</v>
       </c>
       <c r="M19" t="n">
-        <v>0.78</v>
+        <v>5.45</v>
       </c>
       <c r="N19" t="n">
-        <v>3.04</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
         <v>-3.99</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44944.55208333334</v>
+        <v>44945.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>420.35</v>
+        <v>412.15</v>
       </c>
       <c r="I20" t="n">
         <v>415.5903365993065</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>-7.18</v>
+        <v>-8.99</v>
       </c>
       <c r="L20" t="n">
-        <v>8.119999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.18</v>
+        <v>0.8</v>
       </c>
       <c r="N20" t="n">
         <v>4.67</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>6.95</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44950.38541666666</v>
+        <v>44950.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>423.65</v>
+        <v>434</v>
       </c>
       <c r="I21" t="n">
         <v>431.6219701062485</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.79</v>
+        <v>-5.3</v>
       </c>
       <c r="L21" t="n">
-        <v>3.02</v>
+        <v>5.79</v>
       </c>
       <c r="M21" t="n">
         <v>0.47</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.47</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44994.55208333334</v>
+        <v>44995.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>448.7</v>
+        <v>443.3</v>
       </c>
       <c r="I22" t="n">
         <v>446.7883700763462</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>44</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>3.39</v>
+        <v>2.14</v>
       </c>
       <c r="L22" t="n">
         <v>2.53</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.77</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45027.55208333334</v>
+        <v>45028.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>422.25</v>
+        <v>433.95</v>
       </c>
       <c r="I23" t="n">
         <v>432.128645990383</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K23" t="n">
-        <v>4.75</v>
+        <v>2.11</v>
       </c>
       <c r="L23" t="n">
         <v>2.46</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>5.94</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45076.55208333334</v>
+        <v>45077.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>534.7</v>
+        <v>505.8</v>
       </c>
       <c r="I24" t="n">
         <v>514.7833692911312</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K24" t="n">
-        <v>23.22</v>
+        <v>16.56</v>
       </c>
       <c r="L24" t="n">
         <v>2.58</v>
       </c>
       <c r="M24" t="n">
-        <v>0.86</v>
+        <v>4.26</v>
       </c>
       <c r="N24" t="n">
         <v>2.57</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45077.38541666666</v>
+        <v>45077.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>505.8</v>
+        <v>560.65</v>
       </c>
       <c r="I25" t="n">
         <v>548.9500564299909</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-10.84</v>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>13.24</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N25" t="n">
         <v>4.85</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.87</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>594.2</v>
+        <v>566.1</v>
       </c>
       <c r="I26" t="n">
         <v>568.2525482590357</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>5.98</v>
+        <v>0.97</v>
       </c>
       <c r="L26" t="n">
         <v>9.93</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>10.14</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45156.55208333334</v>
+        <v>45159.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>566.8</v>
+        <v>583</v>
       </c>
       <c r="I27" t="n">
         <v>572.5540950869938</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.12</v>
+        <v>-2.99</v>
       </c>
       <c r="L27" t="n">
         <v>6.92</v>
       </c>
       <c r="M27" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
         <v>-4.91</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.99</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45162.55208333334</v>
+        <v>45163.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>589.6</v>
+        <v>580</v>
       </c>
       <c r="I28" t="n">
         <v>582.423679893497</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>1.13</v>
+        <v>-0.51</v>
       </c>
       <c r="L28" t="n">
         <v>2.22</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.09</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>516.7</v>
+        <v>541.35</v>
       </c>
       <c r="I29" t="n">
         <v>536.3030799876632</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K29" t="n">
-        <v>10.91</v>
+        <v>6.66</v>
       </c>
       <c r="L29" t="n">
         <v>6.55</v>
@@ -2094,7 +2441,7 @@
         <v>3.16</v>
       </c>
       <c r="N29" t="n">
-        <v>2.97</v>
+        <v>6.25</v>
       </c>
       <c r="O29" t="n">
         <v>0.01</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.41</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45258.55208333334</v>
+        <v>45259.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>559.1</v>
+        <v>555.6</v>
       </c>
       <c r="I30" t="n">
         <v>556.5156569778803</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K30" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="L30" t="n">
         <v>4.15</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.07</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45266.55208333334</v>
+        <v>45267.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>573</v>
+        <v>582.5</v>
       </c>
       <c r="I31" t="n">
         <v>582.0930584422043</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.13</v>
+        <v>-4.84</v>
       </c>
       <c r="L31" t="n">
         <v>5.38</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>5.79</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>565.2</v>
+        <v>537.8</v>
       </c>
       <c r="I32" t="n">
         <v>549.2304996312668</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.97</v>
+        <v>-7.67</v>
       </c>
       <c r="L32" t="n">
-        <v>5.84</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>0.04</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45282.55208333334</v>
+        <v>45286.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>575.8</v>
+        <v>582.65</v>
       </c>
       <c r="I33" t="n">
         <v>581.5768669187514</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.07</v>
+        <v>-8.34</v>
       </c>
       <c r="L33" t="n">
-        <v>8.01</v>
+        <v>9.67</v>
       </c>
       <c r="M33" t="n">
         <v>0.88</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.44</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45303.55208333334</v>
+        <v>45306.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>605.25</v>
+        <v>602.35</v>
       </c>
       <c r="I34" t="n">
         <v>603.8236460539113</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>3.88</v>
+        <v>3.38</v>
       </c>
       <c r="L34" t="n">
         <v>1.14</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>7.14</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>595.5</v>
+        <v>616</v>
       </c>
       <c r="I35" t="n">
         <v>610.675885443893</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>1.14</v>
+        <v>-2.27</v>
       </c>
       <c r="L35" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="M35" t="n">
         <v>4.26</v>
       </c>
       <c r="N35" t="n">
-        <v>2.26</v>
+        <v>3.85</v>
       </c>
       <c r="O35" t="n">
         <v>-0.95</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>602.5</v>
+        <v>591.55</v>
       </c>
       <c r="I36" t="n">
         <v>597.2014828404639</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.19</v>
+        <v>-3.97</v>
       </c>
       <c r="L36" t="n">
-        <v>4.11</v>
+        <v>5.03</v>
       </c>
       <c r="M36" t="n">
         <v>0.06</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>8.73</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45341.55208333334</v>
+        <v>45342.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>613.95</v>
+        <v>643.4</v>
       </c>
       <c r="I37" t="n">
         <v>629.1250095421119</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.79</v>
+        <v>-8.77</v>
       </c>
       <c r="L37" t="n">
-        <v>5.84</v>
+        <v>10.98</v>
       </c>
       <c r="M37" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="N37" t="n">
         <v>4.97</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>8.24</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>685</v>
+        <v>640.45</v>
       </c>
       <c r="I38" t="n">
         <v>647.9566586571319</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K38" t="n">
-        <v>6.47</v>
+        <v>-0.46</v>
       </c>
       <c r="L38" t="n">
-        <v>5.86</v>
+        <v>6.18</v>
       </c>
       <c r="M38" t="n">
         <v>0.37</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>5.59</v>
       </c>
       <c r="O38" t="n">
         <v>4.24</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.62</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45373.55208333334</v>
+        <v>45377.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>691</v>
+        <v>698.2</v>
       </c>
       <c r="I39" t="n">
         <v>695.5954544890589</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.89</v>
+        <v>-9.02</v>
       </c>
       <c r="L39" t="n">
-        <v>9.1</v>
+        <v>10.03</v>
       </c>
       <c r="M39" t="n">
         <v>1.41</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>9.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45390.38541666666</v>
+        <v>45390.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>649</v>
+        <v>645.9</v>
       </c>
       <c r="I40" t="n">
         <v>646.2271157212921</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.05</v>
+        <v>-7.49</v>
       </c>
       <c r="L40" t="n">
-        <v>7.18</v>
+        <v>7.98</v>
       </c>
       <c r="M40" t="n">
         <v>0.16</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.14</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>603.7</v>
+        <v>612.7</v>
       </c>
       <c r="I41" t="n">
         <v>612.0154071447021</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>6.53</v>
+        <v>5.14</v>
       </c>
       <c r="L41" t="n">
         <v>9.32</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.35</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45503.38541666666</v>
+        <v>45503.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>686.35</v>
+        <v>678.85</v>
       </c>
       <c r="I42" t="n">
         <v>681.8908031763571</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>74</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>12.02</v>
+        <v>10.8</v>
       </c>
       <c r="L42" t="n">
         <v>2.37</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>7.46</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45527.55208333334</v>
+        <v>45530.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>697</v>
+        <v>705.95</v>
       </c>
       <c r="I43" t="n">
         <v>699.6079070771913</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.67</v>
+        <v>-3.99</v>
       </c>
       <c r="L43" t="n">
-        <v>3.44</v>
+        <v>4.29</v>
       </c>
       <c r="M43" t="n">
         <v>2.62</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.73</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>705.8</v>
+        <v>693.45</v>
       </c>
       <c r="I44" t="n">
         <v>696.118557003611</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.02</v>
+        <v>-1.77</v>
       </c>
       <c r="L44" t="n">
         <v>3.96</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45588.55208333334</v>
+        <v>45589.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>638</v>
+        <v>725.4</v>
       </c>
       <c r="I45" t="n">
         <v>669.1342637914832</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>8</v>
+        <v>-4.61</v>
       </c>
       <c r="L45" t="n">
-        <v>2.53</v>
+        <v>6.81</v>
       </c>
       <c r="M45" t="n">
-        <v>1.19</v>
+        <v>4.08</v>
       </c>
       <c r="N45" t="n">
-        <v>1.06</v>
+        <v>14.11</v>
       </c>
       <c r="O45" t="n">
         <v>-1.53</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>12.31</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>681.6</v>
+        <v>664.45</v>
       </c>
       <c r="I46" t="n">
         <v>668.7848823872513</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.04</v>
+        <v>-8.4</v>
       </c>
       <c r="L46" t="n">
-        <v>8.5</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M46" t="n">
         <v>1.01</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.5</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45693.55208333334</v>
+        <v>45694.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>516.9</v>
+        <v>532.25</v>
       </c>
       <c r="I47" t="n">
         <v>521.63486303226</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>84.16666666666667</v>
+        <v>85</v>
       </c>
       <c r="K47" t="n">
-        <v>22.21</v>
+        <v>19.9</v>
       </c>
       <c r="L47" t="n">
         <v>5.5</v>
@@ -3120,7 +3683,7 @@
         <v>2.67</v>
       </c>
       <c r="N47" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="O47" t="n">
         <v>-2.2</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45702.38541666666</v>
+        <v>45702.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>495.7</v>
+        <v>487.95</v>
       </c>
       <c r="I48" t="n">
         <v>491.1529389985693</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.87</v>
+        <v>-8.32</v>
       </c>
       <c r="L48" t="n">
-        <v>7</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M48" t="n">
         <v>0.88</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>509.5</v>
+        <v>523.15</v>
       </c>
       <c r="I49" t="n">
         <v>513.7922628883035</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.42</v>
+        <v>-7.21</v>
       </c>
       <c r="L49" t="n">
-        <v>7.52</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M49" t="n">
         <v>2.66</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.52</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45742.55208333334</v>
+        <v>45743.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>496</v>
+        <v>466.25</v>
       </c>
       <c r="I50" t="n">
         <v>477.3257739943479</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.19</v>
+        <v>-10.88</v>
       </c>
       <c r="L50" t="n">
-        <v>8.06</v>
+        <v>11.5</v>
       </c>
       <c r="M50" t="n">
-        <v>1.46</v>
+        <v>5.24</v>
       </c>
       <c r="N50" t="n">
-        <v>3.66</v>
+        <v>6.02</v>
       </c>
       <c r="O50" t="n">
         <v>1.92</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>430.75</v>
+        <v>460.35</v>
       </c>
       <c r="I51" t="n">
         <v>441.8314833824514</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>7.61</v>
+        <v>1.27</v>
       </c>
       <c r="L51" t="n">
         <v>2.98</v>
@@ -3348,7 +3959,7 @@
         <v>5.34</v>
       </c>
       <c r="N51" t="n">
-        <v>5.85</v>
+        <v>7.43</v>
       </c>
       <c r="O51" t="n">
         <v>-6.02</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.51</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45813.55208333334</v>
+        <v>45814.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>528</v>
+        <v>514.75</v>
       </c>
       <c r="I52" t="n">
         <v>517.5587443773099</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K52" t="n">
-        <v>14.7</v>
+        <v>11.82</v>
       </c>
       <c r="L52" t="n">
         <v>5.32</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.55</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45854.55208333334</v>
+        <v>45855.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>455.75</v>
+        <v>478.75</v>
       </c>
       <c r="I53" t="n">
         <v>471.7102905856481</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>11.46</v>
+        <v>6.99</v>
       </c>
       <c r="L53" t="n">
         <v>3.87</v>
@@ -3462,7 +4097,7 @@
         <v>5.16</v>
       </c>
       <c r="N53" t="n">
-        <v>1.86</v>
+        <v>6.35</v>
       </c>
       <c r="O53" t="n">
         <v>-3.07</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.75</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45867.55208333334</v>
+        <v>45868.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>471.95</v>
+        <v>455.8</v>
       </c>
       <c r="I54" t="n">
         <v>458.9437497328339</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.42</v>
+        <v>-4.79</v>
       </c>
       <c r="L54" t="n">
-        <v>4.9</v>
+        <v>5.07</v>
       </c>
       <c r="M54" t="n">
         <v>0.27</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.6</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45939.38541666666</v>
+        <v>45939.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>422.15</v>
+        <v>429.9</v>
       </c>
       <c r="I55" t="n">
         <v>425.6360080900078</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>71</v>
+        <v>71.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>7.38</v>
+        <v>5.68</v>
       </c>
       <c r="L55" t="n">
         <v>3.5</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.12</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45999.38541666666</v>
+        <v>45999.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="I56" t="n">
         <v>487.6455088620469</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>59.83333333333334</v>
+        <v>60</v>
       </c>
       <c r="K56" t="n">
-        <v>13.75</v>
+        <v>13.05</v>
       </c>
       <c r="L56" t="n">
         <v>1.9</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.43</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46044.38541666666</v>
+        <v>46044.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>463.7</v>
+        <v>470</v>
       </c>
       <c r="I57" t="n">
         <v>466.8069714286526</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>44.83333333333334</v>
+        <v>45</v>
       </c>
       <c r="K57" t="n">
-        <v>4.59</v>
+        <v>3.29</v>
       </c>
       <c r="L57" t="n">
         <v>3.35</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.47</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>533.25</v>
+        <v>508.8</v>
       </c>
       <c r="I58" t="n">
         <v>516.3801076754008</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>36</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K58" t="n">
-        <v>13.46</v>
+        <v>8.26</v>
       </c>
       <c r="L58" t="n">
         <v>4.79</v>
       </c>
       <c r="M58" t="n">
-        <v>1.2</v>
+        <v>5.86</v>
       </c>
       <c r="N58" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="O58" t="n">
         <v>5.71</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.88</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>501.8</v>
+        <v>522</v>
       </c>
       <c r="I59" t="n">
         <v>521.442964344987</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K59" t="n">
-        <v>1.38</v>
+        <v>-2.59</v>
       </c>
       <c r="L59" t="n">
         <v>5.52</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46160.38541666666</v>
+        <v>46160.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>571.7</v>
+        <v>569.1</v>
       </c>
       <c r="I60" t="n">
         <v>570.1376116565918</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>61</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>9.52</v>
+        <v>9.02</v>
       </c>
       <c r="L60" t="n">
         <v>9.1</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.46</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46168.38541666666</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>600.55</v>
+        <v>609</v>
       </c>
       <c r="I61" t="n">
         <v>605.885264207025</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.53</v>
+        <v>-7.01</v>
       </c>
       <c r="L61" t="n">
-        <v>6.15</v>
+        <v>7.12</v>
       </c>
       <c r="M61" t="n">
         <v>0.82</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.01</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>805</v>
+        <v>775.9</v>
       </c>
       <c r="I62" t="n">
         <v>793.0423399137861</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>98</v>
+        <v>98.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>32.18</v>
+        <v>27.41</v>
       </c>
       <c r="L62" t="n">
         <v>4.42</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.32</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46287.55208333334</v>
+        <v>46288.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>806</v>
+        <v>825.1</v>
       </c>
       <c r="I63" t="n">
         <v>813.7195226961406</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.88</v>
+        <v>-6.34</v>
       </c>
       <c r="L63" t="n">
-        <v>5.32</v>
+        <v>6.44</v>
       </c>
       <c r="M63" t="n">
         <v>0.67</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>6.53</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46303.55208333334</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>794.5</v>
+        <v>777.9</v>
       </c>
       <c r="I64" t="n">
         <v>787.1938776149891</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.71</v>
+        <v>-5.72</v>
       </c>
       <c r="L64" t="n">
-        <v>5.02</v>
+        <v>6.13</v>
       </c>
       <c r="M64" t="n">
         <v>0.41</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.34</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>780.5</v>
+        <v>857.5</v>
       </c>
       <c r="I65" t="n">
         <v>805.8345723577265</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.33</v>
+        <v>-10.23</v>
       </c>
       <c r="L65" t="n">
-        <v>5.89</v>
+        <v>11.58</v>
       </c>
       <c r="M65" t="n">
-        <v>0.73</v>
+        <v>3.56</v>
       </c>
       <c r="N65" t="n">
-        <v>3.62</v>
+        <v>8.33</v>
       </c>
       <c r="O65" t="n">
         <v>-1.11</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,12 @@
       <c r="Q66" t="n">
         <v>2</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6308,7 +7105,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.3</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +7115,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6328,7 +7125,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="8">
@@ -6338,7 +7135,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -6348,7 +7145,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="10">
@@ -6358,7 +7155,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60.6</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="11">
@@ -6398,7 +7195,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.12</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="15">
@@ -6408,7 +7205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.23</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="16">
@@ -6418,7 +7215,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.01</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="17">
@@ -6428,7 +7225,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.18</v>
+        <v>27.41</v>
       </c>
     </row>
     <row r="18">
@@ -6438,7 +7235,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.9</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +7245,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.93</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="20">
@@ -6458,7 +7255,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.85</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="21">
@@ -6468,7 +7265,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.93</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="22">
@@ -6478,7 +7275,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -6488,7 +7285,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6498,7 +7295,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.46</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="25">
@@ -6508,7 +7305,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.34</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="26">
@@ -6518,7 +7315,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="27">
@@ -6528,7 +7325,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.720000000000001</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="28">
@@ -6538,7 +7335,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
